--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rjh7012\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DF55A2-D92C-4D59-B33A-B356539E4A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25635275-5B0C-4A47-BC2A-C3E712594BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1A0562BB-97C0-4544-9B95-15B5C8E05E59}"/>
   </bookViews>
@@ -391,7 +391,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -488,31 +488,34 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -857,16 +860,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="2.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -884,24 +887,24 @@
       <c r="W1" s="4"/>
     </row>
     <row r="2" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
       <c r="I2" s="3"/>
       <c r="J2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="K2" s="5"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
@@ -911,26 +914,26 @@
       <c r="W2" s="3"/>
     </row>
     <row r="3" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="34" t="s">
+      <c r="J3" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34" t="s">
+      <c r="K3" s="35"/>
+      <c r="L3" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="3"/>
       <c r="S3" s="7" t="s">
@@ -947,23 +950,23 @@
     </row>
     <row r="4" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="3"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="34" t="s">
+      <c r="J4" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="3"/>
       <c r="S4" s="9"/>
@@ -1103,32 +1106,32 @@
         <v>11</v>
       </c>
       <c r="T9" s="21"/>
-      <c r="U9" s="37" t="s">
+      <c r="U9" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="V9" s="37"/>
-      <c r="W9" s="37"/>
+      <c r="V9" s="32"/>
+      <c r="W9" s="32"/>
     </row>
     <row r="10" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="20"/>
       <c r="B10" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="38"/>
-      <c r="Q10" s="38"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
       <c r="R10" s="3"/>
       <c r="S10" s="29"/>
       <c r="T10" s="3"/>
@@ -1139,21 +1142,21 @@
     <row r="11" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="20"/>
       <c r="B11" s="22"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="37"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
       <c r="R11" s="3"/>
       <c r="S11" s="5"/>
       <c r="T11" s="3"/>
@@ -1166,21 +1169,21 @@
       <c r="B12" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
       <c r="R12" s="3"/>
       <c r="S12" s="29"/>
       <c r="T12" s="3"/>
@@ -1216,21 +1219,21 @@
     <row r="14" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="20"/>
       <c r="B14" s="22"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="38"/>
-      <c r="Q14" s="38"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="37"/>
+      <c r="O14" s="37"/>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="37"/>
       <c r="R14" s="3"/>
       <c r="S14" s="5"/>
       <c r="T14" s="3"/>
@@ -1265,61 +1268,61 @@
     </row>
     <row r="16" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="20"/>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="39"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
       <c r="R16" s="21"/>
       <c r="S16" s="21" t="s">
         <v>11</v>
       </c>
       <c r="T16" s="21"/>
-      <c r="U16" s="37" t="s">
+      <c r="U16" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="V16" s="37"/>
-      <c r="W16" s="37"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
     </row>
     <row r="17" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="20"/>
       <c r="B17" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="38"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="37"/>
       <c r="R17" s="3"/>
       <c r="S17" s="29"/>
       <c r="T17" s="3"/>
-      <c r="U17" s="40"/>
-      <c r="V17" s="40"/>
-      <c r="W17" s="40"/>
+      <c r="U17" s="39"/>
+      <c r="V17" s="39"/>
+      <c r="W17" s="39"/>
     </row>
     <row r="18" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="20"/>
@@ -1344,9 +1347,9 @@
       <c r="R18" s="3"/>
       <c r="S18" s="5"/>
       <c r="T18" s="3"/>
-      <c r="U18" s="36"/>
-      <c r="V18" s="36"/>
-      <c r="W18" s="36"/>
+      <c r="U18" s="38"/>
+      <c r="V18" s="38"/>
+      <c r="W18" s="38"/>
     </row>
     <row r="19" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="20"/>
@@ -1430,26 +1433,16 @@
       <c r="W21" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="U18:W18"/>
+  <mergeCells count="9">
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="J4:K4"/>
     <mergeCell ref="C8:Q8"/>
     <mergeCell ref="B9:Q9"/>
     <mergeCell ref="U9:W9"/>
-    <mergeCell ref="C10:Q10"/>
-    <mergeCell ref="C11:Q11"/>
-    <mergeCell ref="C12:Q12"/>
-    <mergeCell ref="C14:Q14"/>
     <mergeCell ref="B16:Q16"/>
     <mergeCell ref="U16:W16"/>
-    <mergeCell ref="C17:Q17"/>
-    <mergeCell ref="U17:W17"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:P3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:P4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.31" top="0.78740157480314965" bottom="0.59055118110236227" header="0" footer="0.39370078740157483"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -1,36 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rjh7012\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAOS_DS25\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25635275-5B0C-4A47-BC2A-C3E712594BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0A4F5D-E40F-4B75-8A01-1D10FD056266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1A0562BB-97C0-4544-9B95-15B5C8E05E59}"/>
+    <workbookView xWindow="8745" yWindow="30" windowWidth="17970" windowHeight="15285" xr2:uid="{1A0562BB-97C0-4544-9B95-15B5C8E05E59}"/>
   </bookViews>
   <sheets>
     <sheet name="YYYY.MM.DD" sheetId="17" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'YYYY.MM.DD'!$A$1:$W$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">YYYY.MM.DD!$A$1:$R$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -123,7 +114,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>박성철 팀장</t>
+    <t>ㅁㅁㅁ 팀장</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -391,7 +382,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -482,6 +473,24 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -493,27 +502,6 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -537,9 +525,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -577,7 +565,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -683,7 +671,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -825,7 +813,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -833,33 +821,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16203177-6797-4999-A1B4-06E79AB36A88}">
-  <dimension ref="A1:W21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:R21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="0.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="0.83203125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="4.83203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="0.83203125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="4.83203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="0.83203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="4.83203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4.33203125" style="1" customWidth="1"/>
-    <col min="13" max="14" width="0.83203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="4.83203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="3.25" style="1" customWidth="1"/>
-    <col min="17" max="17" width="1.25" style="1" customWidth="1"/>
-    <col min="18" max="18" width="0.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="47" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="0.83203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="24.75" style="2" customWidth="1"/>
-    <col min="22" max="22" width="0.83203125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="24.75" style="2" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="0.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.875" style="1" customWidth="1"/>
+    <col min="3" max="7" width="4.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="4.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="3.25" style="1" customWidth="1"/>
+    <col min="12" max="12" width="1.25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="0.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="47" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="0.875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="24.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="0.875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="24.75" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="2.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:18" ht="2.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
@@ -868,8 +850,8 @@
       <c r="D1" s="34"/>
       <c r="E1" s="34"/>
       <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -877,166 +859,136 @@
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-    </row>
-    <row r="2" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+    </row>
+    <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34"/>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
       <c r="D2" s="34"/>
       <c r="E2" s="34"/>
       <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="5" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="6"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-    </row>
-    <row r="3" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34"/>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
       <c r="D3" s="34"/>
       <c r="E3" s="34"/>
       <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="35" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="35"/>
-      <c r="L3" s="41" t="s">
+      <c r="I3" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="7" t="s">
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="T3" s="7"/>
-      <c r="U3" s="8" t="s">
+      <c r="O3" s="7"/>
+      <c r="P3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8" t="s">
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="35" t="s">
+      <c r="H4" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="35"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="10"/>
-    </row>
-    <row r="5" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="10"/>
+    </row>
+    <row r="5" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
+      <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="I5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="13"/>
-    </row>
-    <row r="6" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L5" s="6"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="13"/>
+    </row>
+    <row r="6" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="14"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
+      <c r="E6" s="14"/>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="17"/>
-    </row>
-    <row r="7" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="17"/>
+    </row>
+    <row r="7" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="6"/>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -1047,151 +999,121 @@
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19"/>
-    </row>
-    <row r="8" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+    </row>
+    <row r="8" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-    </row>
-    <row r="9" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+    </row>
+    <row r="9" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20"/>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21" t="s">
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="T9" s="21"/>
-      <c r="U9" s="32" t="s">
+      <c r="O9" s="21"/>
+      <c r="P9" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="V9" s="32"/>
-      <c r="W9" s="32"/>
-    </row>
-    <row r="10" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+    </row>
+    <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20"/>
       <c r="B10" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="24"/>
-    </row>
-    <row r="11" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+    </row>
+    <row r="11" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20"/>
       <c r="B11" s="22"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-    </row>
-    <row r="12" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+    </row>
+    <row r="12" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20"/>
       <c r="B12" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="25"/>
-    </row>
-    <row r="13" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+    </row>
+    <row r="13" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20"/>
       <c r="B13" s="22"/>
       <c r="C13" s="3"/>
@@ -1205,43 +1127,33 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
+      <c r="N13" s="5"/>
       <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="25"/>
-      <c r="W13" s="25"/>
-    </row>
-    <row r="14" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P13" s="5"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+    </row>
+    <row r="14" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20"/>
       <c r="B14" s="22"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="37"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="25"/>
-    </row>
-    <row r="15" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+    </row>
+    <row r="15" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20"/>
       <c r="B15" s="22"/>
       <c r="C15" s="23"/>
@@ -1254,77 +1166,62 @@
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-    </row>
-    <row r="16" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+    </row>
+    <row r="16" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20"/>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="21" t="s">
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="T16" s="21"/>
-      <c r="U16" s="32" t="s">
+      <c r="O16" s="21"/>
+      <c r="P16" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="V16" s="32"/>
-      <c r="W16" s="32"/>
-    </row>
-    <row r="17" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+    </row>
+    <row r="17" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20"/>
       <c r="B17" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="39"/>
-      <c r="V17" s="39"/>
-      <c r="W17" s="39"/>
-    </row>
-    <row r="18" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+    </row>
+    <row r="18" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20"/>
       <c r="B18" s="26" t="s">
         <v>17</v>
@@ -1339,19 +1236,14 @@
       <c r="J18" s="23"/>
       <c r="K18" s="23"/>
       <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="38"/>
-      <c r="V18" s="38"/>
-      <c r="W18" s="38"/>
-    </row>
-    <row r="19" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M18" s="3"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="27"/>
+    </row>
+    <row r="19" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20"/>
       <c r="B19" s="26" t="s">
         <v>18</v>
@@ -1366,19 +1258,14 @@
       <c r="J19" s="23"/>
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="5"/>
       <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-    </row>
-    <row r="20" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P19" s="27"/>
+      <c r="Q19" s="27"/>
+      <c r="R19" s="27"/>
+    </row>
+    <row r="20" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="20"/>
       <c r="B20" s="26" t="s">
         <v>19</v>
@@ -1393,19 +1280,14 @@
       <c r="J20" s="23"/>
       <c r="K20" s="23"/>
       <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="5"/>
       <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-    </row>
-    <row r="21" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="27"/>
+    </row>
+    <row r="21" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20"/>
       <c r="B21" s="26" t="s">
         <v>20</v>
@@ -1420,29 +1302,22 @@
       <c r="J21" s="23"/>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="5"/>
       <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="27"/>
-      <c r="V21" s="27"/>
-      <c r="W21" s="27"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="27"/>
+      <c r="R21" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C8:Q8"/>
-    <mergeCell ref="B9:Q9"/>
-    <mergeCell ref="U9:W9"/>
-    <mergeCell ref="B16:Q16"/>
-    <mergeCell ref="U16:W16"/>
+  <mergeCells count="7">
+    <mergeCell ref="B9:L9"/>
+    <mergeCell ref="P9:R9"/>
+    <mergeCell ref="B16:L16"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="A1:F3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="C8:L8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.31" top="0.78740157480314965" bottom="0.59055118110236227" header="0" footer="0.39370078740157483"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAOS_DS25\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0A4F5D-E40F-4B75-8A01-1D10FD056266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503AF5B2-FD2F-44DC-A37A-C69A382EACF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8745" yWindow="30" windowWidth="17970" windowHeight="15285" xr2:uid="{1A0562BB-97C0-4544-9B95-15B5C8E05E59}"/>
+    <workbookView xWindow="7740" yWindow="975" windowWidth="17970" windowHeight="15285" xr2:uid="{1A0562BB-97C0-4544-9B95-15B5C8E05E59}"/>
   </bookViews>
   <sheets>
     <sheet name="YYYY.MM.DD" sheetId="17" r:id="rId1"/>
@@ -382,7 +382,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -485,6 +485,9 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -494,16 +497,10 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -842,14 +839,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="2.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -864,12 +861,12 @@
       <c r="R1" s="4"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
       <c r="G2" s="3"/>
       <c r="H2" s="5" t="s">
         <v>1</v>
@@ -886,14 +883,14 @@
       <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="34"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="33" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="33" t="s">
@@ -917,13 +914,13 @@
     </row>
     <row r="4" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="33" t="s">
         <v>6</v>
       </c>
       <c r="I4" s="33"/>
@@ -1006,16 +1003,16 @@
     <row r="8" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -1025,29 +1022,29 @@
     </row>
     <row r="9" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20"/>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
       <c r="M9" s="21"/>
       <c r="N9" s="21" t="s">
         <v>11</v>
       </c>
       <c r="O9" s="21"/>
-      <c r="P9" s="38" t="s">
+      <c r="P9" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="38"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
     </row>
     <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20"/>
@@ -1193,11 +1190,11 @@
         <v>11</v>
       </c>
       <c r="O16" s="21"/>
-      <c r="P16" s="38" t="s">
+      <c r="P16" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="Q16" s="38"/>
-      <c r="R16" s="38"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
     </row>
     <row r="17" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20"/>
@@ -1310,10 +1307,8 @@
       <c r="R21" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B9:L9"/>
+  <mergeCells count="5">
     <mergeCell ref="P9:R9"/>
-    <mergeCell ref="B16:L16"/>
     <mergeCell ref="P16:R16"/>
     <mergeCell ref="A1:F3"/>
     <mergeCell ref="B4:E4"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAOS_DS25\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503AF5B2-FD2F-44DC-A37A-C69A382EACF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6923142-7081-4AB7-B507-DDB2079684AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7740" yWindow="975" windowWidth="17970" windowHeight="15285" xr2:uid="{1A0562BB-97C0-4544-9B95-15B5C8E05E59}"/>
+    <workbookView xWindow="8475" yWindow="120" windowWidth="17970" windowHeight="15285" xr2:uid="{1A0562BB-97C0-4544-9B95-15B5C8E05E59}"/>
   </bookViews>
   <sheets>
     <sheet name="YYYY.MM.DD" sheetId="17" r:id="rId1"/>
@@ -485,7 +485,10 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -497,10 +500,7 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -839,14 +839,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="2.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -861,12 +861,12 @@
       <c r="R1" s="4"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="A2" s="36"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
       <c r="G2" s="3"/>
       <c r="H2" s="5" t="s">
         <v>1</v>
@@ -883,12 +883,12 @@
       <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
+      <c r="A3" s="36"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="3"/>
       <c r="H3" s="33" t="s">
         <v>2</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="4" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="33" t="s">
@@ -1003,16 +1003,16 @@
     <row r="8" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -1022,29 +1022,29 @@
     </row>
     <row r="9" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20"/>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="21"/>
       <c r="N9" s="21" t="s">
         <v>11</v>
       </c>
       <c r="O9" s="21"/>
-      <c r="P9" s="34" t="s">
+      <c r="P9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
+      <c r="Q9" s="39"/>
+      <c r="R9" s="39"/>
     </row>
     <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20"/>
@@ -1172,29 +1172,29 @@
     </row>
     <row r="16" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20"/>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
       <c r="M16" s="21"/>
       <c r="N16" s="21" t="s">
         <v>11</v>
       </c>
       <c r="O16" s="21"/>
-      <c r="P16" s="34" t="s">
+      <c r="P16" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
+      <c r="Q16" s="39"/>
+      <c r="R16" s="39"/>
     </row>
     <row r="17" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20"/>
@@ -1307,9 +1307,7 @@
       <c r="R21" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="P9:R9"/>
-    <mergeCell ref="P16:R16"/>
+  <mergeCells count="3">
     <mergeCell ref="A1:F3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="C8:L8"/>
